--- a/AIAcademyPlaywrightFramework/src/test/resources/TestData/LoginData.xlsx
+++ b/AIAcademyPlaywrightFramework/src/test/resources/TestData/LoginData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Email</t>
   </si>
@@ -54,7 +54,10 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>ExpectedMessage</t>
+  </si>
+  <si>
+    <t>Invalid email or password</t>
   </si>
 </sst>
 </file>
@@ -404,15 +407,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,8 +426,11 @@
       <c r="C1" t="s">
         <v>9</v>
       </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -434,7 +441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -445,7 +452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -453,10 +460,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>

--- a/AIAcademyPlaywrightFramework/src/test/resources/TestData/LoginData.xlsx
+++ b/AIAcademyPlaywrightFramework/src/test/resources/TestData/LoginData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>Email</t>
   </si>
@@ -48,16 +48,10 @@
     <t>ExpectedResult</t>
   </si>
   <si>
-    <t>Testing@1235</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
     <t>ExpectedMessage</t>
-  </si>
-  <si>
-    <t>Invalid email or password</t>
   </si>
 </sst>
 </file>
@@ -427,7 +421,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -438,7 +432,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -449,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -457,13 +451,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -474,7 +465,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
